--- a/problem3_summary.xlsx
+++ b/problem3_summary.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="120" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="240" uniqueCount="30">
   <si>
     <t>Row</t>
   </si>
@@ -155,12 +155,12 @@
   <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.86328125" customWidth="true"/>
-    <col min="2" max="2" width="11.796875" customWidth="true"/>
-    <col min="3" max="3" width="11.796875" customWidth="true"/>
-    <col min="4" max="4" width="11.796875" customWidth="true"/>
-    <col min="5" max="5" width="11.796875" customWidth="true"/>
-    <col min="6" max="6" width="11.796875" customWidth="true"/>
+    <col min="1" max="1" width="11.7109375" customWidth="true"/>
+    <col min="2" max="2" width="11.7109375" customWidth="true"/>
+    <col min="3" max="3" width="11.7109375" customWidth="true"/>
+    <col min="4" max="4" width="11.7109375" customWidth="true"/>
+    <col min="5" max="5" width="11.7109375" customWidth="true"/>
+    <col min="6" max="6" width="11.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -672,12 +672,12 @@
   <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.86328125" customWidth="true"/>
-    <col min="2" max="2" width="12.796875" customWidth="true"/>
-    <col min="3" max="3" width="12.796875" customWidth="true"/>
-    <col min="4" max="4" width="12.796875" customWidth="true"/>
-    <col min="5" max="5" width="12.796875" customWidth="true"/>
-    <col min="6" max="6" width="14.3984375" customWidth="true"/>
+    <col min="1" max="1" width="11.7109375" customWidth="true"/>
+    <col min="2" max="2" width="12.7109375" customWidth="true"/>
+    <col min="3" max="3" width="12.7109375" customWidth="true"/>
+    <col min="4" max="4" width="12.7109375" customWidth="true"/>
+    <col min="5" max="5" width="12.7109375" customWidth="true"/>
+    <col min="6" max="6" width="14.42578125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1189,12 +1189,12 @@
   <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.86328125" customWidth="true"/>
-    <col min="2" max="2" width="12.796875" customWidth="true"/>
-    <col min="3" max="3" width="12.796875" customWidth="true"/>
-    <col min="4" max="4" width="12.796875" customWidth="true"/>
-    <col min="5" max="5" width="12.796875" customWidth="true"/>
-    <col min="6" max="6" width="12.796875" customWidth="true"/>
+    <col min="1" max="1" width="11.7109375" customWidth="true"/>
+    <col min="2" max="2" width="12.7109375" customWidth="true"/>
+    <col min="3" max="3" width="12.7109375" customWidth="true"/>
+    <col min="4" max="4" width="12.7109375" customWidth="true"/>
+    <col min="5" max="5" width="12.7109375" customWidth="true"/>
+    <col min="6" max="6" width="12.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1706,12 +1706,12 @@
   <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.86328125" customWidth="true"/>
-    <col min="2" max="2" width="14.796875" customWidth="true"/>
-    <col min="3" max="3" width="14.796875" customWidth="true"/>
-    <col min="4" max="4" width="15.33203125" customWidth="true"/>
-    <col min="5" max="5" width="15.33203125" customWidth="true"/>
-    <col min="6" max="6" width="15.33203125" customWidth="true"/>
+    <col min="1" max="1" width="11.7109375" customWidth="true"/>
+    <col min="2" max="2" width="14.7109375" customWidth="true"/>
+    <col min="3" max="3" width="14.7109375" customWidth="true"/>
+    <col min="4" max="4" width="15.5703125" customWidth="true"/>
+    <col min="5" max="5" width="15.5703125" customWidth="true"/>
+    <col min="6" max="6" width="15.5703125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
